--- a/Test Project/TestUI/document/TranVietHai.xlsx
+++ b/Test Project/TestUI/document/TranVietHai.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="133">
   <si>
     <t>Scenario ID</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>Search Box (</t>
     </r>
     <r>
@@ -93,6 +99,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">'; DROP TABLE Stocks; </t>
     </r>
     <r>
@@ -134,6 +146,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>?page=-1</t>
     </r>
     <r>
@@ -166,6 +184,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>-10</t>
     </r>
     <r>
@@ -195,6 +219,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF444746"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>9999999999999999</t>
     </r>
     <r>
@@ -265,27 +295,7 @@
     <t>Verify search against XSS and SQL Injection</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">User is logged in and on </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.../Admin/Stock</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.</t>
-    </r>
+    <t>User is logged in and on .../Admin/Stock.</t>
   </si>
   <si>
     <r>
@@ -307,8 +317,7 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> into the search box. 
-2. Click the 'Tìm kiếm' button.</t>
+      <t xml:space="preserve"> into the search box.</t>
     </r>
   </si>
   <si>
@@ -321,15 +330,16 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>2. Click the 'Tìm kiếm' button.</t>
+  </si>
+  <si>
     <t>TC_STK_02</t>
   </si>
   <si>
     <t>Verify search with an extremely long string (Stress Test)</t>
   </si>
   <si>
-    <t>1. Generate a string of 5000 'A' characters. 
-2. Enter the string into the search box. 
-3. Click 'Tìm kiếm'.</t>
+    <t>1. Generate a string of 5000 'A' characters.</t>
   </si>
   <si>
     <t>System truncates the string or returns "Not found", without throwing a 500 Server Error.</t>
@@ -338,70 +348,19 @@
     <t>Request processed without crashing.</t>
   </si>
   <si>
+    <t>2. Enter the string into the search box.</t>
+  </si>
+  <si>
+    <t>3. Click 'Tìm kiếm'.</t>
+  </si>
+  <si>
     <t>TC_STK_03</t>
   </si>
   <si>
     <t>Verify pagination with negative Page Size via DOM manipulation</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. Use DevTools to inject an option with value </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> into the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>pageSize</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> dropdown. 
-2. Select the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> option and submit the form.</t>
-    </r>
+    <t>1. Use DevTools to inject an option with value -5 into the pageSize dropdown.</t>
   </si>
   <si>
     <t>Backend blocks the negative value and falls back to a default value (e.g., 10), preventing divide-by-zero errors.</t>
@@ -410,6 +369,9 @@
     <t>Value rejected; URL reloaded safely.</t>
   </si>
   <si>
+    <t>2. Select the -5 option and submit the form.</t>
+  </si>
+  <si>
     <t>TC_STK_04</t>
   </si>
   <si>
@@ -419,46 +381,7 @@
     <t>User is logged in.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. Navigate directly to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.../Admin/Stock?page=-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">. 
-2. Navigate directly to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.../Admin/Stock?page=999999</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.</t>
-    </r>
+    <t>1. Navigate directly to .../Admin/Stock?page=-1.</t>
   </si>
   <si>
     <t>System does not crash. It gracefully handles the error by displaying "Không có dữ liệu" or redirecting.</t>
@@ -467,6 +390,9 @@
     <t>Empty state handled correctly without crash.</t>
   </si>
   <si>
+    <t>2. Navigate directly to .../Admin/Stock?page=999999.</t>
+  </si>
+  <si>
     <t>TC_PUR_01</t>
   </si>
   <si>
@@ -476,70 +402,10 @@
     <t>Verify form submission with negative Quantity and Unit Cost</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">User is on </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.../Admin/Purchases/Create</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Select a Supplier and Product.
-2. Enter </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> in Qty and </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-50000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> in Unit Cost. 
-3. Click Submit.</t>
-    </r>
+    <t>User is on .../Admin/Purchases/Create.</t>
+  </si>
+  <si>
+    <t>1. Select a Supplier and Product.</t>
   </si>
   <si>
     <t>The system blocks the submission (Frontend or Backend validation) and displays an error message.</t>
@@ -548,76 +414,31 @@
     <t>Form blocked from saving to database.</t>
   </si>
   <si>
+    <t>2. Enter -10 in Qty and -50000 in Unit Cost.</t>
+  </si>
+  <si>
+    <t>3. Click Submit.</t>
+  </si>
+  <si>
     <t>TC_PUR_02</t>
   </si>
   <si>
     <t>Verify Backend validation when Frontend HTML5 validation is bypassed</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. Remove </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>required</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>min</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>max</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> attributes from the form using DevTools. 
-2. Click Submit with an empty form.</t>
-    </r>
+    <t>1. Remove required, min, max attributes from the form using DevTools.</t>
   </si>
   <si>
     <t>ASP.NET Core ModelState catches the empty fields and returns validation errors without a 500 Crash.</t>
   </si>
   <si>
-    <t>Validation error displayed; no server crash.</t>
+    <t>A red error notification bar appears, but it is completely empty (no validation text is displayed).</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>2. Click Submit with an empty form.</t>
   </si>
   <si>
     <t>TC_PUR_03</t>
@@ -626,91 +447,16 @@
     <t>Verify system behavior against Numeric Overflow</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. Enter </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>9999999999999999</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> in Qty. 
-2. Enter </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>9999999999</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> in Unit Cost. 
-3. Click Submit.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">System handles the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>FormatException</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>OverflowException</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> gracefully, displaying a "Value too large" message instead of crashing.</t>
-    </r>
-  </si>
-  <si>
-    <t>Error handled gracefully.</t>
+    <t>1. Enter 9999999999999999 in Qty.</t>
+  </si>
+  <si>
+    <t>System handles the FormatException or OverflowException gracefully, displaying a "Value too large" message instead of crashing.</t>
+  </si>
+  <si>
+    <t>A red error notification bar appears, but it is completely empty (no error message text is displayed).</t>
+  </si>
+  <si>
+    <t>2. Enter 999999999999 in Unit Cost.</t>
   </si>
   <si>
     <t>TC_PUR_04</t>
@@ -722,46 +468,7 @@
     <t>System has existing purchases.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. Navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.../Admin/Purchases/Details/-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">. 
-2. Navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.../Admin/Purchases/Details/999999</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.</t>
-    </r>
+    <t>1. Navigate to .../Admin/Purchases/Details/-1.</t>
   </si>
   <si>
     <t>The system returns a friendly 404/Not Found page for both scenarios.</t>
@@ -770,6 +477,9 @@
     <t>404 page displayed.</t>
   </si>
   <si>
+    <t>2. Navigate to .../Admin/Purchases/Details/999999.</t>
+  </si>
+  <si>
     <t>TC_SUP_01</t>
   </si>
   <si>
@@ -779,58 +489,19 @@
     <t>Verify uniqueness constraint on Supplier Email</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">A supplier with email </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>autotest@ncc.local</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> exists. User is on Create page.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Fill all fields validly. 
-2. Enter </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>autotest@ncc.local</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> in the Email field. 
-3. Click Submit.</t>
-    </r>
+    <t>A supplier with email autotest@ncc.local exists. User is on Create page.</t>
+  </si>
+  <si>
+    <t>1. Fill all fields validly.</t>
   </si>
   <si>
     <t>Backend checks the database and blocks creation, displaying an "Email already exists" error.</t>
   </si>
   <si>
-    <t>Creation blocked due to Unique constraint.</t>
+    <t>System did not throw an error and successfully created a new supplier with the duplicate email.</t>
+  </si>
+  <si>
+    <t>2. Enter autotest@ncc.local in the Email field.</t>
   </si>
   <si>
     <t>TC_SUP_02</t>
@@ -842,34 +513,16 @@
     <t>User is on Create page.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. Use DevTools to remove </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>required</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> attributes from all inputs. 
-2. Click Submit with empty fields.</t>
-    </r>
+    <t>1. Use DevTools to remove required attributes from all inputs.</t>
   </si>
   <si>
     <t>Backend validates the model state and returns the UI with validation error messages, preventing a crash.</t>
   </si>
   <si>
     <t>Validation errors shown.</t>
+  </si>
+  <si>
+    <t>2. Click Submit with empty fields.</t>
   </si>
   <si>
     <t>TC_SUP_03</t>
@@ -897,8 +550,18 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> in Name. 
-2. Enter </t>
+      <t xml:space="preserve"> in Name.</t>
+    </r>
+  </si>
+  <si>
+    <t>System sanitizes malicious code. Alert does not trigger and DB remains intact.</t>
+  </si>
+  <si>
+    <t>Malicious code sanitized to normal string.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Enter </t>
     </r>
     <r>
       <rPr>
@@ -916,53 +579,23 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> in Address. 
-3. Click Submit.</t>
+      <t xml:space="preserve"> in Address.</t>
     </r>
   </si>
   <si>
-    <t>System sanitizes malicious code. Alert does not trigger and DB remains intact.</t>
-  </si>
-  <si>
-    <t>Malicious code sanitized to normal string.</t>
-  </si>
-  <si>
     <t>TC_SUP_04</t>
   </si>
   <si>
     <t>Verify URL manipulation with invalid Supplier ID</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. Navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF444746"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.../Admin/Suppliers/Details/-999</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>.</t>
-    </r>
+    <t>1. Navigate to .../Admin/Suppliers/Details/-999.</t>
   </si>
   <si>
     <t>Application displays a user-friendly 404 Not Found error page.</t>
   </si>
   <si>
-    <t>The system failed to display a 404 page or friendly error UI when an invalid ID was passed</t>
-  </si>
-  <si>
-    <t>FAILED</t>
+    <t>System successfully displays a user-friendly 404 Not Found error page.</t>
   </si>
 </sst>
 </file>
@@ -970,8 +603,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
@@ -1003,7 +636,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1012,14 +644,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1057,13 +689,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -1072,52 +697,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1139,6 +728,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -1146,6 +765,20 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1156,43 +789,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1204,67 +957,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1276,72 +969,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1365,6 +998,43 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="FF1F1F1F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F1F1F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F1F1F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F1F1F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F1F1F"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F1F1F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F1F1F"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1F1F1F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1376,17 +1046,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1415,32 +1074,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1464,6 +1104,36 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -1482,15 +1152,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1500,134 +1170,134 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1637,34 +1307,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1999,58 +1675,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" ht="27.6" spans="1:4">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="15"/>
     </row>
     <row r="3" ht="27.6" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="10"/>
+      <c r="D3" s="15"/>
     </row>
     <row r="4" ht="27.6" spans="1:4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="15"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2071,114 +1747,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="9" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="12" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="11">
         <v>-5</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="12" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="12" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="12" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="12" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2191,7 +1867,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12.1111111111111" customWidth="1"/>
@@ -2201,7 +1877,7 @@
     <col min="5" max="5" width="42.8888888888889" customWidth="1"/>
     <col min="6" max="6" width="43.3333333333333" customWidth="1"/>
     <col min="7" max="7" width="39.8888888888889" customWidth="1"/>
-    <col min="8" max="8" width="7.55555555555556" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.15" spans="1:8">
@@ -2230,7 +1906,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" ht="55.95" spans="1:8">
+    <row r="2" ht="42.9" customHeight="1" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>49</v>
       </c>
@@ -2256,293 +1932,724 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" ht="42.15" spans="1:8">
-      <c r="A3" s="1" t="s">
+    <row r="3" ht="15.15" spans="1:8">
+      <c r="A3" s="1"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" ht="15.15" spans="1:8">
+      <c r="A4" s="1"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" ht="15.9" customHeight="1" spans="1:8">
+      <c r="A5" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" ht="42.15" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" ht="42.15" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" ht="42.15" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" ht="42.15" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" ht="42.15" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" ht="42.15" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" ht="42.15" spans="1:8">
+    <row r="6" ht="15.15" spans="1:8">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" ht="15.15" spans="1:8">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" ht="15.15" spans="1:8">
+      <c r="A8" s="1"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" ht="15.15" spans="1:8">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" ht="29.1" customHeight="1" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" ht="42.15" spans="1:8">
-      <c r="A11" s="1" t="s">
+    <row r="11" ht="15.15" spans="1:8">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" ht="15.15" spans="1:8">
+      <c r="A12" s="1"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" ht="15.9" customHeight="1" spans="1:8">
+      <c r="A13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" ht="15.15" spans="1:8">
+      <c r="A14" s="1"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" ht="28.35" spans="1:8">
+      <c r="A15" s="1"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" ht="15.9" customHeight="1" spans="1:8">
+      <c r="A16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" ht="15.15" spans="1:8">
+      <c r="A17" s="1"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" ht="15.15" spans="1:8">
+      <c r="A18" s="1"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" ht="15.15" spans="1:8">
+      <c r="A19" s="1"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" ht="15.15" spans="1:8">
+      <c r="A20" s="1"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" ht="29.1" customHeight="1" spans="1:8">
+      <c r="A21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" ht="15.15" spans="1:8">
+      <c r="A22" s="1"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" ht="15.15" spans="1:8">
+      <c r="A23" s="1"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24" ht="15.9" customHeight="1" spans="1:8">
+      <c r="A24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" ht="15.15" spans="1:8">
+      <c r="A25" s="1"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" ht="15.15" spans="1:8">
+      <c r="A26" s="1"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+    </row>
+    <row r="27" ht="15.15" spans="1:8">
+      <c r="A27" s="1"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" ht="15.15" spans="1:8">
+      <c r="A28" s="1"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+    </row>
+    <row r="29" ht="15.9" customHeight="1" spans="1:8">
+      <c r="A29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="H29" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" ht="15.15" spans="1:8">
+      <c r="A30" s="1"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" ht="28.35" spans="1:8">
+      <c r="A31" s="1"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" ht="15.9" customHeight="1" spans="1:8">
+      <c r="A32" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="C32" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" ht="15.15" spans="1:8">
+      <c r="A33" s="1"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+    </row>
+    <row r="34" ht="15.15" spans="1:8">
+      <c r="A34" s="1"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+    </row>
+    <row r="35" ht="15.15" spans="1:8">
+      <c r="A35" s="1"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+    </row>
+    <row r="36" ht="15.15" spans="1:8">
+      <c r="A36" s="1"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+    </row>
+    <row r="37" ht="29.1" customHeight="1" spans="1:8">
+      <c r="A37" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" ht="69.75" spans="1:8">
-      <c r="A12" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H12" s="2" t="s">
+    <row r="38" ht="15.15" spans="1:8">
+      <c r="A38" s="1"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" ht="15.15" spans="1:8">
+      <c r="A39" s="1"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" ht="29.1" customHeight="1" spans="1:8">
+      <c r="A40" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" ht="42.15" spans="1:8">
-      <c r="A13" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>119</v>
+    <row r="41" ht="15.15" spans="1:8">
+      <c r="A41" s="1"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" ht="28.35" spans="1:8">
+      <c r="A42" s="1"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" ht="15.15" spans="1:8">
+      <c r="A43" s="1"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" ht="15.15" spans="1:8">
+      <c r="A44" s="1"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" ht="28.35" spans="1:8">
+      <c r="A45" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="77">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A16:A20"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A40:A44"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B16:B20"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B44"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C9"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="C16:C20"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C24:C28"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="C40:C44"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D5:D9"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="D16:D20"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="D32:D36"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="D40:D44"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="F5:F9"/>
+    <mergeCell ref="F10:F12"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="F16:F20"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="F24:F28"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="F32:F36"/>
+    <mergeCell ref="F37:F39"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="G5:G9"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="G16:G20"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="G24:G28"/>
+    <mergeCell ref="G29:G31"/>
+    <mergeCell ref="G32:G36"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="H5:H9"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="H16:H20"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="H24:H28"/>
+    <mergeCell ref="H29:H31"/>
+    <mergeCell ref="H32:H36"/>
+    <mergeCell ref="H37:H39"/>
+    <mergeCell ref="H40:H44"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
